--- a/SLA Report Template.xlsx
+++ b/SLA Report Template.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="178" documentId="13_ncr:1_{4B083F3C-1079-44B5-8F5D-AB5C435395D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61E21B7B-C1A8-4047-B054-92B7E9BD0CB8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B78EEE-C3ED-4DE9-95CA-207A9E2C0541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="7" r:id="rId1"/>
     <sheet name="Prototypes" sheetId="3" r:id="rId2"/>
     <sheet name="50% Reviews" sheetId="2" r:id="rId3"/>
     <sheet name="PSIAs" sheetId="1" r:id="rId4"/>
-    <sheet name="Peer Verifications" sheetId="4" r:id="rId5"/>
+    <sheet name="Peer Reviews" sheetId="4" r:id="rId5"/>
     <sheet name="Holidays" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -143,9 +143,6 @@
     <t>SLA Report - Prototype Reviews (2 Business Days)</t>
   </si>
   <si>
-    <t>SLA Report - Peer Verifications (3 Business Days)</t>
-  </si>
-  <si>
     <t>This sheet lists the current observed holidays for BYU so that the calculation doesn’t take them into account when calculating days overdue.</t>
   </si>
   <si>
@@ -165,6 +162,9 @@
   </si>
   <si>
     <t>This Month's SLA Report Overview</t>
+  </si>
+  <si>
+    <t>SLA Report - Peer Reviews (3 Business Days)</t>
   </si>
 </sst>
 </file>
@@ -1708,7 +1708,7 @@
   <sheetData>
     <row r="4" spans="2:6" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" s="23"/>
       <c r="D4" s="23"/>
@@ -1717,11 +1717,11 @@
     </row>
     <row r="8" spans="2:6" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B8" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" s="22"/>
       <c r="E8" s="22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F8" s="22"/>
     </row>
@@ -1837,11 +1837,11 @@
     </row>
     <row r="19" spans="2:6" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B19" s="22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C19" s="22"/>
       <c r="E19" s="22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F19" s="22"/>
     </row>
@@ -1935,7 +1935,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="4" t="e">
-        <f>AVERAGE('Peer Verifications'!E3:E18)</f>
+        <f>AVERAGE('Peer Reviews'!E3:E18)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -11562,7 +11562,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="27.75" x14ac:dyDescent="0.4">
       <c r="A1" s="24" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -15159,7 +15159,7 @@
     </row>
     <row r="2" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="1"/>
@@ -15169,7 +15169,7 @@
     </row>
     <row r="3" spans="1:12" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="27"/>
       <c r="C3" s="1"/>
@@ -15291,7 +15291,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="19">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="D11" s="2"/>
       <c r="G11" s="2"/>
@@ -15302,7 +15302,7 @@
         <v>27</v>
       </c>
       <c r="B12" s="19">
-        <v>45862</v>
+        <v>46227</v>
       </c>
       <c r="D12" s="2"/>
       <c r="G12" s="2"/>
@@ -15313,7 +15313,7 @@
         <v>28</v>
       </c>
       <c r="B13" s="19">
-        <v>45901</v>
+        <v>46272</v>
       </c>
       <c r="D13" s="2"/>
       <c r="G13" s="2"/>
@@ -15324,7 +15324,7 @@
         <v>29</v>
       </c>
       <c r="B14" s="19">
-        <v>45988</v>
+        <v>46352</v>
       </c>
       <c r="D14" s="2"/>
       <c r="G14" s="2"/>
@@ -15335,7 +15335,7 @@
         <v>30</v>
       </c>
       <c r="B15" s="19">
-        <v>45989</v>
+        <v>46353</v>
       </c>
       <c r="D15" s="2"/>
       <c r="G15" s="2"/>
@@ -15346,7 +15346,7 @@
         <v>31</v>
       </c>
       <c r="B16" s="19">
-        <v>46016</v>
+        <v>46380</v>
       </c>
       <c r="D16" s="2"/>
       <c r="G16" s="2"/>
@@ -15357,7 +15357,7 @@
         <v>32</v>
       </c>
       <c r="B17" s="19">
-        <v>46017</v>
+        <v>46381</v>
       </c>
       <c r="D17" s="2"/>
       <c r="G17" s="2"/>
